--- a/ert/input/distributions/design_matrix_one_by_one_exercise_04a.xlsx
+++ b/ert/input/distributions/design_matrix_one_by_one_exercise_04a.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="DesignSheet01" sheetId="1" state="visible" r:id="rId2"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="99">
   <si>
     <t xml:space="preserve">REAL</t>
   </si>
@@ -257,18 +257,6 @@
     <t xml:space="preserve">THERYS_APS_1_0_GF_GRF1_TREND_STACKANGLE</t>
   </si>
   <si>
-    <t xml:space="preserve">THERYS_APS_1_0_GF_GRF2_RESIDUAL_MAINRANGE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THERYS_APS_1_0_GF_GRF2_RESIDUAL_PERPRANGE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THERYS_APS_1_0_GF_GRF2_RESIDUAL_VERTRANGE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THERYS_APS_1_0_GF_GRF2_RESIDUAL_AZIMUTHANGLE</t>
-  </si>
-  <si>
     <t xml:space="preserve">THERYS_APS_1_0_GF_GRF3_RESIDUAL_MAINRANGE</t>
   </si>
   <si>
@@ -291,18 +279,6 @@
   </si>
   <si>
     <t xml:space="preserve">VOLON_APS_1_0_GF_GRF1_RESIDUAL_AZIMUTHANGLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VOLON_APS_1_0_GF_GRF2_RESIDUAL_MAINRANGE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VOLON_APS_1_0_GF_GRF2_RESIDUAL_PERPRANGE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VOLON_APS_1_0_GF_GRF2_RESIDUAL_VERTRANGE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VOLON_APS_1_0_GF_GRF2_RESIDUAL_AZIMUTHANGLE</t>
   </si>
   <si>
     <t xml:space="preserve">VOLON_APS_1_0_GF_GRF3_RESIDUAL_MAINRANGE</t>
@@ -348,8 +324,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="0.00"/>
+    <numFmt numFmtId="166" formatCode="0.000000000"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -452,13 +431,21 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -473,18 +460,30 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="false"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3" customBuiltin="false"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6" customBuiltin="false"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4" customBuiltin="false"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7" customBuiltin="false"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5" customBuiltin="false"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -550,12 +549,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J26"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.23"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.11"/>
@@ -567,7 +566,6 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="22.41"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="21.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="21.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="11" style="0" width="8.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -778,10 +776,10 @@
       <c r="E7" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="2" t="n">
         <v>1675.5559117125</v>
       </c>
-      <c r="G7" s="0" t="n">
+      <c r="G7" s="2" t="n">
         <v>1662.89416903477</v>
       </c>
       <c r="H7" s="0" t="n">
@@ -810,10 +808,10 @@
       <c r="E8" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8" s="2" t="n">
         <v>1672.99731935747</v>
       </c>
-      <c r="G8" s="0" t="n">
+      <c r="G8" s="2" t="n">
         <v>1661.25662999352</v>
       </c>
       <c r="H8" s="0" t="n">
@@ -842,10 +840,10 @@
       <c r="E9" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="0" t="n">
+      <c r="F9" s="2" t="n">
         <v>1678.90712660919</v>
       </c>
-      <c r="G9" s="0" t="n">
+      <c r="G9" s="2" t="n">
         <v>1660.37670054972</v>
       </c>
       <c r="H9" s="0" t="n">
@@ -874,10 +872,10 @@
       <c r="E10" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="0" t="n">
+      <c r="F10" s="2" t="n">
         <v>1681.32912758434</v>
       </c>
-      <c r="G10" s="0" t="n">
+      <c r="G10" s="2" t="n">
         <v>1660.50920148136</v>
       </c>
       <c r="H10" s="0" t="n">
@@ -906,10 +904,10 @@
       <c r="E11" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="0" t="n">
+      <c r="F11" s="2" t="n">
         <v>1681.96333654218</v>
       </c>
-      <c r="G11" s="0" t="n">
+      <c r="G11" s="2" t="n">
         <v>1660.56768836073</v>
       </c>
       <c r="H11" s="0" t="n">
@@ -938,10 +936,10 @@
       <c r="E12" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="0" t="n">
+      <c r="F12" s="2" t="n">
         <v>1678.13921724197</v>
       </c>
-      <c r="G12" s="0" t="n">
+      <c r="G12" s="2" t="n">
         <v>1659.4958913139</v>
       </c>
       <c r="H12" s="0" t="n">
@@ -970,10 +968,10 @@
       <c r="E13" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="0" t="n">
+      <c r="F13" s="2" t="n">
         <v>1673.66489814036</v>
       </c>
-      <c r="G13" s="0" t="n">
+      <c r="G13" s="2" t="n">
         <v>1657.57859182616</v>
       </c>
       <c r="H13" s="0" t="n">
@@ -1002,10 +1000,10 @@
       <c r="E14" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="F14" s="0" t="n">
+      <c r="F14" s="2" t="n">
         <v>1681.30570778487</v>
       </c>
-      <c r="G14" s="0" t="n">
+      <c r="G14" s="2" t="n">
         <v>1663.84336193793</v>
       </c>
       <c r="H14" s="0" t="n">
@@ -1034,10 +1032,10 @@
       <c r="E15" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="0" t="n">
+      <c r="F15" s="2" t="n">
         <v>1674.49044731467</v>
       </c>
-      <c r="G15" s="0" t="n">
+      <c r="G15" s="2" t="n">
         <v>1656.52566235947</v>
       </c>
       <c r="H15" s="0" t="n">
@@ -1066,10 +1064,10 @@
       <c r="E16" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="0" t="n">
+      <c r="F16" s="2" t="n">
         <v>1677.894816726</v>
       </c>
-      <c r="G16" s="0" t="n">
+      <c r="G16" s="2" t="n">
         <v>1655.17076867762</v>
       </c>
       <c r="H16" s="0" t="n">
@@ -1104,13 +1102,13 @@
       <c r="G17" s="0" t="n">
         <v>1660</v>
       </c>
-      <c r="H17" s="0" t="n">
+      <c r="H17" s="3" t="n">
         <v>0.0205733727700444</v>
       </c>
-      <c r="I17" s="0" t="n">
+      <c r="I17" s="3" t="n">
         <v>0.000320542216220237</v>
       </c>
-      <c r="J17" s="0" t="n">
+      <c r="J17" s="3" t="n">
         <v>0.368299015431535</v>
       </c>
     </row>
@@ -1136,13 +1134,13 @@
       <c r="G18" s="0" t="n">
         <v>1660</v>
       </c>
-      <c r="H18" s="0" t="n">
+      <c r="H18" s="3" t="n">
         <v>0.00208783440910858</v>
       </c>
-      <c r="I18" s="0" t="n">
+      <c r="I18" s="3" t="n">
         <v>0.0114384901291924</v>
       </c>
-      <c r="J18" s="0" t="n">
+      <c r="J18" s="3" t="n">
         <v>0.0215729763535966</v>
       </c>
     </row>
@@ -1168,13 +1166,13 @@
       <c r="G19" s="0" t="n">
         <v>1660</v>
       </c>
-      <c r="H19" s="0" t="n">
+      <c r="H19" s="3" t="n">
         <v>1.49052720990459E-005</v>
       </c>
-      <c r="I19" s="0" t="n">
+      <c r="I19" s="3" t="n">
         <v>0.0128688366579841</v>
       </c>
-      <c r="J19" s="0" t="n">
+      <c r="J19" s="3" t="n">
         <v>0.0391127177424503</v>
       </c>
     </row>
@@ -1200,13 +1198,13 @@
       <c r="G20" s="0" t="n">
         <v>1660</v>
       </c>
-      <c r="H20" s="0" t="n">
+      <c r="H20" s="3" t="n">
         <v>7.47786906251625E-005</v>
       </c>
-      <c r="I20" s="0" t="n">
+      <c r="I20" s="3" t="n">
         <v>0.00688448972257132</v>
       </c>
-      <c r="J20" s="0" t="n">
+      <c r="J20" s="3" t="n">
         <v>0.00158357825058025</v>
       </c>
     </row>
@@ -1232,13 +1230,13 @@
       <c r="G21" s="0" t="n">
         <v>1660</v>
       </c>
-      <c r="H21" s="0" t="n">
+      <c r="H21" s="3" t="n">
         <v>0.0211266753202807</v>
       </c>
-      <c r="I21" s="0" t="n">
+      <c r="I21" s="3" t="n">
         <v>0.0111362535109171</v>
       </c>
-      <c r="J21" s="0" t="n">
+      <c r="J21" s="3" t="n">
         <v>0.000178328067672858</v>
       </c>
     </row>
@@ -1264,13 +1262,13 @@
       <c r="G22" s="0" t="n">
         <v>1660</v>
       </c>
-      <c r="H22" s="0" t="n">
+      <c r="H22" s="3" t="n">
         <v>0.0100401673607205</v>
       </c>
-      <c r="I22" s="0" t="n">
+      <c r="I22" s="3" t="n">
         <v>0.00881101282192947</v>
       </c>
-      <c r="J22" s="0" t="n">
+      <c r="J22" s="3" t="n">
         <v>0.158833263442751</v>
       </c>
     </row>
@@ -1296,13 +1294,13 @@
       <c r="G23" s="0" t="n">
         <v>1660</v>
       </c>
-      <c r="H23" s="0" t="n">
+      <c r="H23" s="3" t="n">
         <v>1.35015174362279E-005</v>
       </c>
-      <c r="I23" s="0" t="n">
+      <c r="I23" s="3" t="n">
         <v>0.000460599883180768</v>
       </c>
-      <c r="J23" s="0" t="n">
+      <c r="J23" s="3" t="n">
         <v>0.000917017238373426</v>
       </c>
     </row>
@@ -1328,13 +1326,13 @@
       <c r="G24" s="0" t="n">
         <v>1660</v>
       </c>
-      <c r="H24" s="0" t="n">
+      <c r="H24" s="3" t="n">
         <v>0.00105127245192242</v>
       </c>
-      <c r="I24" s="0" t="n">
+      <c r="I24" s="3" t="n">
         <v>0.00131758908684925</v>
       </c>
-      <c r="J24" s="0" t="n">
+      <c r="J24" s="3" t="n">
         <v>3.32545673039523E-005</v>
       </c>
     </row>
@@ -1360,13 +1358,13 @@
       <c r="G25" s="0" t="n">
         <v>1660</v>
       </c>
-      <c r="H25" s="0" t="n">
+      <c r="H25" s="3" t="n">
         <v>0.0455944052626558</v>
       </c>
-      <c r="I25" s="0" t="n">
+      <c r="I25" s="3" t="n">
         <v>0.000525456048334634</v>
       </c>
-      <c r="J25" s="0" t="n">
+      <c r="J25" s="3" t="n">
         <v>0.0907039976275258</v>
       </c>
     </row>
@@ -1392,13 +1390,13 @@
       <c r="G26" s="0" t="n">
         <v>1660</v>
       </c>
-      <c r="H26" s="0" t="n">
+      <c r="H26" s="3" t="n">
         <v>0.000119024775887912</v>
       </c>
-      <c r="I26" s="0" t="n">
+      <c r="I26" s="3" t="n">
         <v>0.370879729618053</v>
       </c>
-      <c r="J26" s="0" t="n">
+      <c r="J26" s="3" t="n">
         <v>0.0652652747252486</v>
       </c>
     </row>
@@ -1414,31 +1412,30 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B100"/>
-  <sheetFormatPr defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:B1048576"/>
+  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="5.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="3" style="0" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9.91"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="3" t="n">
+      <c r="B1" s="5" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1859,98 +1856,98 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4" t="s">
+      <c r="A55" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B55" s="0" t="n">
+      <c r="B55" s="7" t="n">
         <v>2000</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="s">
+      <c r="A56" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B56" s="0" t="n">
+      <c r="B56" s="7" t="n">
         <v>400</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="4" t="s">
+      <c r="A57" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B57" s="0" t="n">
+      <c r="B57" s="7" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="4" t="s">
+      <c r="A58" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B58" s="0" t="n">
+      <c r="B58" s="7" t="n">
         <v>70</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="4" t="s">
+      <c r="A59" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B59" s="0" t="n">
+      <c r="B59" s="7" t="n">
         <v>1000</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="4" t="s">
+      <c r="A60" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B60" s="0" t="n">
+      <c r="B60" s="7" t="n">
         <v>1000</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="4" t="s">
+      <c r="A61" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B61" s="0" t="n">
+      <c r="B61" s="8" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="4" t="s">
+      <c r="A62" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B62" s="0" t="n">
+      <c r="B62" s="8" t="n">
         <v>70</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="4" t="s">
+      <c r="A63" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B63" s="0" t="n">
+      <c r="B63" s="8" t="n">
         <v>1000</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="4" t="s">
+      <c r="A64" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B64" s="0" t="n">
+      <c r="B64" s="8" t="n">
         <v>1000</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="4" t="s">
+      <c r="A65" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B65" s="0" t="n">
-        <v>5</v>
+      <c r="B65" s="8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="4" t="s">
+      <c r="A66" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B66" s="0" t="n">
+      <c r="B66" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1958,23 +1955,23 @@
       <c r="A67" s="0" t="s">
         <v>73</v>
       </c>
-      <c r="B67" s="0" t="n">
-        <v>1000</v>
+      <c r="B67" s="7" t="n">
+        <v>3000</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
         <v>74</v>
       </c>
-      <c r="B68" s="0" t="n">
-        <v>6000</v>
+      <c r="B68" s="7" t="n">
+        <v>1500</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
         <v>75</v>
       </c>
-      <c r="B69" s="0" t="n">
+      <c r="B69" s="7" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1982,15 +1979,15 @@
       <c r="A70" s="0" t="s">
         <v>76</v>
       </c>
-      <c r="B70" s="0" t="n">
-        <v>300</v>
+      <c r="B70" s="7" t="n">
+        <v>280</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
         <v>77</v>
       </c>
-      <c r="B71" s="0" t="n">
+      <c r="B71" s="7" t="n">
         <v>0.015</v>
       </c>
     </row>
@@ -1998,31 +1995,31 @@
       <c r="A72" s="0" t="s">
         <v>78</v>
       </c>
-      <c r="B72" s="0" t="n">
-        <v>6000</v>
+      <c r="B72" s="7" t="n">
+        <v>1500</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
         <v>79</v>
       </c>
-      <c r="B73" s="0" t="n">
-        <v>1000</v>
+      <c r="B73" s="7" t="n">
+        <v>1500</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
         <v>80</v>
       </c>
-      <c r="B74" s="0" t="n">
-        <v>5</v>
+      <c r="B74" s="7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
         <v>81</v>
       </c>
-      <c r="B75" s="0" t="n">
+      <c r="B75" s="7" t="n">
         <v>10</v>
       </c>
     </row>
@@ -2030,96 +2027,96 @@
       <c r="A76" s="0" t="s">
         <v>82</v>
       </c>
-      <c r="B76" s="0" t="n">
-        <v>1500</v>
+      <c r="B76" s="7" t="n">
+        <v>900</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
         <v>83</v>
       </c>
-      <c r="B77" s="0" t="n">
-        <v>1500</v>
+      <c r="B77" s="7" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
         <v>84</v>
       </c>
-      <c r="B78" s="0" t="n">
-        <v>1</v>
+      <c r="B78" s="7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="s">
         <v>85</v>
       </c>
-      <c r="B79" s="0" t="n">
-        <v>10</v>
+      <c r="B79" s="7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
         <v>86</v>
       </c>
-      <c r="B80" s="0" t="n">
-        <v>900</v>
+      <c r="B80" s="7" t="n">
+        <v>800</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="0" t="s">
         <v>87</v>
       </c>
-      <c r="B81" s="0" t="n">
-        <v>200</v>
+      <c r="B81" s="7" t="n">
+        <v>800</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="s">
         <v>88</v>
       </c>
-      <c r="B82" s="0" t="n">
-        <v>5</v>
+      <c r="B82" s="7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="0" t="s">
         <v>89</v>
       </c>
-      <c r="B83" s="0" t="n">
-        <v>5</v>
+      <c r="B83" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="0" t="s">
+      <c r="A84" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="B84" s="0" t="n">
-        <v>1000</v>
+      <c r="B84" s="10" t="n">
+        <v>0.34</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="0" t="s">
+      <c r="A85" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B85" s="0" t="n">
-        <v>1000</v>
+      <c r="B85" s="10" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="0" t="s">
+      <c r="A86" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="B86" s="0" t="n">
-        <v>5</v>
+      <c r="B86" s="10" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="0" t="s">
+      <c r="A87" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="B87" s="0" t="n">
-        <v>0</v>
+      <c r="B87" s="10" t="n">
+        <v>0.62</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2127,7 +2124,7 @@
         <v>94</v>
       </c>
       <c r="B88" s="0" t="n">
-        <v>800</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2135,7 +2132,7 @@
         <v>95</v>
       </c>
       <c r="B89" s="0" t="n">
-        <v>800</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2151,81 +2148,25 @@
         <v>97</v>
       </c>
       <c r="B91" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="5" t="s">
+      <c r="A92" s="0" t="s">
         <v>98</v>
       </c>
       <c r="B92" s="0" t="n">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B93" s="0" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="B94" s="0" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="B95" s="0" t="n">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="0" t="s">
-        <v>102</v>
-      </c>
-      <c r="B96" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="0" t="s">
-        <v>103</v>
-      </c>
-      <c r="B97" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="0" t="s">
-        <v>104</v>
-      </c>
-      <c r="B98" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="0" t="s">
-        <v>105</v>
-      </c>
-      <c r="B99" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="0" t="s">
-        <v>106</v>
-      </c>
-      <c r="B100" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555555" footer="0.511805555555555"/>
